--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487082_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487082_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.8077</v>
+        <v>4.7535</v>
       </c>
       <c r="E2" t="n">
-        <v>2.6562</v>
+        <v>3.7359</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1514</v>
+        <v>1.0176</v>
       </c>
       <c r="G2" t="n">
         <v>-1.0611</v>
@@ -610,13 +610,13 @@
         <v>4.6322</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2664</v>
+        <v>0.6795</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8354</v>
+        <v>0.2443</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5691000000000001</v>
+        <v>0.4352</v>
       </c>
       <c r="V2" t="n">
         <v>3.398</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5053</v>
+        <v>2.381</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9712</v>
+        <v>0.4893</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5341</v>
+        <v>1.8916</v>
       </c>
       <c r="G3" t="n">
         <v>-0.2893</v>
@@ -688,13 +688,13 @@
         <v>3.6672</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4086</v>
+        <v>1.2843</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9016</v>
+        <v>0.4198</v>
       </c>
       <c r="U3" t="n">
-        <v>1.507</v>
+        <v>0.8645</v>
       </c>
       <c r="V3" t="n">
         <v>0.614</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0993</v>
+        <v>1.2543</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.2301</v>
+        <v>-0.6105</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3294</v>
+        <v>1.8648</v>
       </c>
       <c r="G4" t="n">
         <v>0.5564</v>
@@ -766,13 +766,13 @@
         <v>3.4741</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.322</v>
+        <v>-0.1669</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.85</v>
+        <v>-0.2303</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.472</v>
+        <v>0.0634</v>
       </c>
       <c r="V4" t="n">
         <v>0.2859</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0959</v>
+        <v>0.7225</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9054</v>
+        <v>-0.3858</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0013</v>
+        <v>1.1083</v>
       </c>
       <c r="G5" t="n">
         <v>0.8837</v>
@@ -844,13 +844,13 @@
         <v>3.0881</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7601</v>
+        <v>-0.1335</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6715</v>
+        <v>-0.152</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0886</v>
+        <v>0.0185</v>
       </c>
       <c r="V5" t="n">
         <v>-1.1857</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0248</v>
+        <v>-1.005</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.5533</v>
+        <v>-1.4531</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5285</v>
+        <v>0.4482</v>
       </c>
       <c r="G6" t="n">
         <v>0.5279</v>
@@ -922,13 +922,13 @@
         <v>0.386</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0086</v>
+        <v>0.0112</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.238</v>
+        <v>-0.1378</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2294</v>
+        <v>0.149</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2835</v>
+        <v>-1.1566</v>
       </c>
       <c r="E7" t="n">
-        <v>0.422</v>
+        <v>0.2812</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7055</v>
+        <v>-1.4378</v>
       </c>
       <c r="G7" t="n">
         <v>2.7746</v>
@@ -1000,13 +1000,13 @@
         <v>1.9301</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3702</v>
+        <v>0.4971</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7099</v>
+        <v>0.5691000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3398</v>
+        <v>-0.0721</v>
       </c>
       <c r="V7" t="n">
         <v>-2.4982</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3754</v>
+        <v>-1.6887</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.525</v>
+        <v>-2.0257</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1496</v>
+        <v>0.337</v>
       </c>
       <c r="G8" t="n">
         <v>-1.8604</v>
@@ -1078,13 +1078,13 @@
         <v>1.7371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6128</v>
+        <v>0.2994</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6954</v>
+        <v>0.1947</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.08260000000000001</v>
+        <v>0.1048</v>
       </c>
       <c r="V8" t="n">
         <v>-0.8999</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3632</v>
+        <v>-1.81</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.9367</v>
+        <v>-2.5173</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5735</v>
+        <v>0.7073</v>
       </c>
       <c r="G9" t="n">
         <v>-3.2974</v>
@@ -1156,13 +1156,13 @@
         <v>2.1231</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3708</v>
+        <v>0.9241</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0278</v>
+        <v>0.4472</v>
       </c>
       <c r="U9" t="n">
-        <v>0.343</v>
+        <v>0.4769</v>
       </c>
       <c r="V9" t="n">
         <v>0.3704</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.8034</v>
+        <v>-4.1723</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2544</v>
+        <v>-3.4359</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.549</v>
+        <v>-0.7364000000000001</v>
       </c>
       <c r="G10" t="n">
         <v>-2.4108</v>
@@ -1234,13 +1234,13 @@
         <v>3.0881</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2756</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.078</v>
+        <v>-0.2594</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3536</v>
+        <v>0.1662</v>
       </c>
       <c r="V10" t="n">
         <v>-2.8263</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2526</v>
+        <v>-4.9813</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9235</v>
+        <v>-3.4648</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3291</v>
+        <v>-1.5165</v>
       </c>
       <c r="G11" t="n">
         <v>-3.377</v>
@@ -1312,13 +1312,13 @@
         <v>1.9301</v>
       </c>
       <c r="S11" t="n">
-        <v>1.3597</v>
+        <v>0.6309</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8276</v>
+        <v>0.2862</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5321</v>
+        <v>0.3447</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2702</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.5947</v>
+        <v>-5.7026</v>
       </c>
       <c r="E12" t="n">
-        <v>-10.279</v>
+        <v>-9.386699999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>3.6842</v>
+        <v>3.684100000000002</v>
       </c>
       <c r="G12" t="n">
         <v>-7.553399999999999</v>
@@ -1390,13 +1390,13 @@
         <v>26.0561</v>
       </c>
       <c r="S12" t="n">
-        <v>3.0406</v>
+        <v>3.9329</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4893999999999998</v>
+        <v>1.3818</v>
       </c>
       <c r="U12" t="n">
-        <v>2.5512</v>
+        <v>2.5511</v>
       </c>
       <c r="V12" t="n">
         <v>-4.012</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.1291</v>
+        <v>7.3627</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9641</v>
+        <v>1.0643</v>
       </c>
       <c r="F13" t="n">
-        <v>6.165</v>
+        <v>6.2985</v>
       </c>
       <c r="G13" t="n">
         <v>5.8351</v>
@@ -1468,13 +1468,13 @@
         <v>4.0532</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2366</v>
+        <v>-0.003</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6279</v>
+        <v>-0.5276999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3912</v>
+        <v>0.5248</v>
       </c>
       <c r="V13" t="n">
         <v>5.1977</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. QUINCY-JONES</t>
+          <t>D. GARCIA CARRERA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.0607</v>
+        <v>4.6553</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7127</v>
+        <v>2.3242</v>
       </c>
       <c r="F14" t="n">
-        <v>3.3481</v>
+        <v>2.331</v>
       </c>
       <c r="G14" t="n">
-        <v>5.7273</v>
+        <v>-0.1001</v>
       </c>
       <c r="H14" t="n">
-        <v>3.7766</v>
+        <v>2.8795</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9507</v>
+        <v>-2.9796</v>
       </c>
       <c r="J14" t="n">
-        <v>3.9776</v>
+        <v>0.8587</v>
       </c>
       <c r="K14" t="n">
-        <v>2.6752</v>
+        <v>2.2924</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3024</v>
+        <v>-1.4337</v>
       </c>
       <c r="M14" t="n">
-        <v>1.7497</v>
+        <v>-0.9588</v>
       </c>
       <c r="N14" t="n">
-        <v>1.1014</v>
+        <v>0.5871</v>
       </c>
       <c r="O14" t="n">
-        <v>0.6483</v>
+        <v>-1.5459</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.386</v>
+        <v>0.386</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.0881</v>
+        <v>-4.0532</v>
       </c>
       <c r="R14" t="n">
-        <v>2.7021</v>
+        <v>4.4392</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2333</v>
+        <v>-0.1299</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4627</v>
+        <v>-0.2085</v>
       </c>
       <c r="U14" t="n">
-        <v>0.696</v>
+        <v>0.0786</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.5138</v>
+        <v>4.4993</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2859</v>
+        <v>5.7272</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.7997</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.5089</v>
+        <v>4.3043</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1859</v>
+        <v>0.286</v>
       </c>
       <c r="F15" t="n">
-        <v>3.323</v>
+        <v>4.0183</v>
       </c>
       <c r="G15" t="n">
         <v>1.0123</v>
@@ -1624,13 +1624,13 @@
         <v>2.5091</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0668</v>
+        <v>-0.2713</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6411</v>
+        <v>-0.541</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4257</v>
+        <v>0.2697</v>
       </c>
       <c r="V15" t="n">
         <v>2.2123</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. GARCIA CARRERA</t>
+          <t>A. QUINCY-JONES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.4724</v>
+        <v>3.9728</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0238</v>
+        <v>0.8128</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4486</v>
+        <v>3.16</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1001</v>
+        <v>5.7273</v>
       </c>
       <c r="H16" t="n">
-        <v>2.8795</v>
+        <v>3.7766</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.9796</v>
+        <v>1.9507</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8587</v>
+        <v>3.9776</v>
       </c>
       <c r="K16" t="n">
-        <v>2.2924</v>
+        <v>2.6752</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.4337</v>
+        <v>1.3024</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9588</v>
+        <v>1.7497</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5871</v>
+        <v>1.1014</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.5459</v>
+        <v>0.6483</v>
       </c>
       <c r="P16" t="n">
-        <v>0.386</v>
+        <v>-0.386</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.0532</v>
+        <v>-3.0881</v>
       </c>
       <c r="R16" t="n">
-        <v>4.4392</v>
+        <v>2.7021</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.3127</v>
+        <v>0.1454</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5089</v>
+        <v>-0.3625</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8038</v>
+        <v>0.5079</v>
       </c>
       <c r="V16" t="n">
-        <v>4.4993</v>
+        <v>-1.5138</v>
       </c>
       <c r="W16" t="n">
-        <v>5.7272</v>
+        <v>0.2859</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.228</v>
+        <v>-1.7997</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.0158</v>
+        <v>2.6507</v>
       </c>
       <c r="E17" t="n">
-        <v>3.9323</v>
+        <v>4.0324</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.9165</v>
+        <v>-1.3817</v>
       </c>
       <c r="G17" t="n">
         <v>2.5339</v>
@@ -1780,13 +1780,13 @@
         <v>2.5091</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.6485</v>
+        <v>-1.0136</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6411</v>
+        <v>-0.541</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.0074</v>
+        <v>-0.4726</v>
       </c>
       <c r="V17" t="n">
         <v>-1.1857</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.316</v>
+        <v>-1.7281</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4538</v>
+        <v>-2.2563</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7698</v>
+        <v>0.5282</v>
       </c>
       <c r="G18" t="n">
         <v>-1.8436</v>
@@ -1858,13 +1858,13 @@
         <v>2.8951</v>
       </c>
       <c r="S18" t="n">
-        <v>3.3876</v>
+        <v>1.3435</v>
       </c>
       <c r="T18" t="n">
-        <v>2.4589</v>
+        <v>0.6564</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9286</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="V18" t="n">
         <v>-1.228</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.9068</v>
+        <v>-3.4663</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.9194</v>
+        <v>-3.7191</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0126</v>
+        <v>0.2529</v>
       </c>
       <c r="G19" t="n">
         <v>-4.0195</v>
@@ -1936,13 +1936,13 @@
         <v>2.3161</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7595</v>
+        <v>-0.3189</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5221</v>
+        <v>-0.3219</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2373</v>
+        <v>0.0029</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2859</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. GOMEZ MERODIO</t>
+          <t>H. SAIZ-BUSTAMANTE GOMEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.6505</v>
+        <v>-4.3825</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.6365</v>
+        <v>-2.7922</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.014</v>
+        <v>-1.5903</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0037</v>
+        <v>-0.5883</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2629</v>
+        <v>1.2317</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.2667</v>
+        <v>-1.82</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.171</v>
+        <v>0.252</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0828</v>
+        <v>1.5058</v>
       </c>
       <c r="L20" t="n">
         <v>-1.2538</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1673</v>
+        <v>-0.8403</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1801</v>
+        <v>-0.2741</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0129</v>
+        <v>-0.5662</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.3511</v>
+        <v>-1.7371</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9301</v>
+        <v>-3.8602</v>
       </c>
       <c r="R20" t="n">
-        <v>0.579</v>
+        <v>2.1231</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1679</v>
+        <v>-0.501</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5354</v>
+        <v>-0.3698</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3675</v>
+        <v>-0.1312</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.1278</v>
+        <v>-1.5561</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.1857</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.1278</v>
+        <v>-2.7418</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>H. SAIZ-BUSTAMANTE GOMEZ</t>
+          <t>J. GOMEZ MERODIO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.3509</v>
+        <v>-4.7715</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.4932</v>
+        <v>-3.4362</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8576</v>
+        <v>-1.3353</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5883</v>
+        <v>-1.0037</v>
       </c>
       <c r="H21" t="n">
-        <v>1.2317</v>
+        <v>0.2629</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.82</v>
+        <v>-1.2667</v>
       </c>
       <c r="J21" t="n">
-        <v>0.252</v>
+        <v>-1.171</v>
       </c>
       <c r="K21" t="n">
-        <v>1.5058</v>
+        <v>0.0828</v>
       </c>
       <c r="L21" t="n">
         <v>-1.2538</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8403</v>
+        <v>0.1673</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2741</v>
+        <v>0.1801</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5662</v>
+        <v>-0.0129</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.7371</v>
+        <v>-1.3511</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.8602</v>
+        <v>-1.9301</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1231</v>
+        <v>0.579</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4694</v>
+        <v>-0.2889</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0708</v>
+        <v>-0.3351</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3986</v>
+        <v>0.0462</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.5561</v>
+        <v>-2.1278</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1857</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.7418</v>
+        <v>-2.1278</v>
       </c>
     </row>
     <row r="22">
@@ -2125,16 +2125,16 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>6.594699999999999</v>
+        <v>8.597399999999997</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.684099999999999</v>
+        <v>-3.684100000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>10.279</v>
+        <v>12.2816</v>
       </c>
       <c r="G22" t="n">
-        <v>7.5534</v>
+        <v>7.553399999999998</v>
       </c>
       <c r="H22" t="n">
         <v>16.4251</v>
@@ -2161,7 +2161,7 @@
         <v>-6.4263</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.930199999999999</v>
+        <v>-1.9302</v>
       </c>
       <c r="Q22" t="n">
         <v>-26.056</v>
@@ -2170,16 +2170,16 @@
         <v>24.126</v>
       </c>
       <c r="S22" t="n">
-        <v>-3.0405</v>
+        <v>-1.0377</v>
       </c>
       <c r="T22" t="n">
         <v>-2.5511</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4895000000000002</v>
+        <v>1.5133</v>
       </c>
       <c r="V22" t="n">
-        <v>4.012</v>
+        <v>4.011999999999999</v>
       </c>
       <c r="W22" t="n">
         <v>14.1119</v>
